--- a/design/mechanical/tender/bom/NIGHTWATCH_tender_BOM.xlsx
+++ b/design/mechanical/tender/bom/NIGHTWATCH_tender_BOM.xlsx
@@ -1263,7 +1263,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Roof span/length = P.ENCLOSURE (ASSUMED footprint); member size ASSUMED design-intent.</t>
+          <t>Roof span/length = P.ENCLOSURE (ASSUMED footprint); 4 perimeter members; size ASSUMED design-intent.</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>261.14</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>179.36</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>HSS 50.8 mm (2.000 in) sq x 3.2 mm (0.125 in) wall x 12000.0 mm (472.441 in)</t>
+          <t>HSS 50.8 mm (2.000 in) sq x 3.2 mm (0.125 in) wall x 3000.0 mm (118.110 in)</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Rectangular roll-off roof frame. Member sizing to be confirmed vs ASCE 7 snow/wind by PE.</t>
+          <t>Rectangular roll-off roof frame (4 perimeter members). Sizing to be confirmed vs ASCE 7 snow/wind by PE.</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>HSS 38.1 mm (1.500 in) sq x 3.2 mm (0.125 in) wall x 15000.0 mm (590.551 in)</t>
+          <t>HSS 38.1 mm (1.500 in) sq x 3.2 mm (0.125 in) wall x 3000.0 mm (118.110 in)</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>261.14</t>
+          <t>52.23</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>HSS 63.5 mm (2.500 in) sq x 4.0 mm (0.157 in) wall x 12000.0 mm (472.441 in)</t>
+          <t>HSS 63.5 mm (2.500 in) sq x 4.0 mm (0.157 in) wall x 6000.0 mm (236.220 in)</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>179.36</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
